--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="66">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,6 +73,36 @@
     <t>2026-05-14</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1189 Дупница</t>
+  </si>
+  <si>
     <t>СB6072HO</t>
   </si>
   <si>
@@ -94,19 +127,73 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>00:12</t>
-  </si>
-  <si>
-    <t>17:41</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>16:33</t>
-  </si>
-  <si>
-    <t>19:47</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>00:12:00</t>
+  </si>
+  <si>
+    <t>17:41:00</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>16:33:00</t>
+  </si>
+  <si>
+    <t>19:47:00</t>
+  </si>
+  <si>
+    <t>13:51:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>13:28:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>17:55:00</t>
+  </si>
+  <si>
+    <t>16:21:00</t>
+  </si>
+  <si>
+    <t>3231283984 3231283984</t>
+  </si>
+  <si>
+    <t>3231514465 3231514465</t>
+  </si>
+  <si>
+    <t>3231728061 3231728061</t>
+  </si>
+  <si>
+    <t>3231780109 3231780109</t>
+  </si>
+  <si>
+    <t>3231876168 3231876168</t>
+  </si>
+  <si>
+    <t>3232052558 3232052558</t>
+  </si>
+  <si>
+    <t>3232064489 3232064489</t>
+  </si>
+  <si>
+    <t>3232197324 3232197324</t>
+  </si>
+  <si>
+    <t>3232200655 3232200655</t>
+  </si>
+  <si>
+    <t>3232208202 3232208202</t>
+  </si>
+  <si>
+    <t>3232481719 3232481719</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ</t>
@@ -530,24 +617,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -587,303 +676,585 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1902</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>34.81</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
         <v>1.78</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>61.96</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.78</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>61.96</v>
       </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>165682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1148</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>22.6</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
         <v>1.78</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>40.23</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.78</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>40.23</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>202837</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1148</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>44</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
         <v>1.46</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>64.23999999999999</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>67.76000000000001</v>
       </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>204472</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1148</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>28.02</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5">
         <v>1.74</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>48.75</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.79</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>50.16</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>205155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>1902</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>40.9</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
         <v>1.75</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>71.58</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>73.62</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <v>28.26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>1.75</v>
+      </c>
+      <c r="I7" s="1">
+        <v>49.46</v>
+      </c>
+      <c r="J7">
+        <v>1.8</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50.87</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>20434</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8">
+        <v>26.19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8">
+        <v>1.76</v>
+      </c>
+      <c r="I8" s="1">
+        <v>46.09</v>
+      </c>
+      <c r="J8">
+        <v>1.81</v>
+      </c>
+      <c r="K8" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9">
+        <v>34.94</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>1.76</v>
+      </c>
+      <c r="I9" s="1">
+        <v>61.49</v>
+      </c>
+      <c r="J9">
+        <v>1.81</v>
+      </c>
+      <c r="K9" s="1">
+        <v>63.24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10">
+        <v>43.16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
+        <v>1.52</v>
+      </c>
+      <c r="I10" s="1">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.57</v>
+      </c>
+      <c r="K10" s="1">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="L6">
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>26.26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11">
+        <v>1.52</v>
+      </c>
+      <c r="I11" s="1">
+        <v>39.92</v>
+      </c>
+      <c r="J11">
+        <v>1.57</v>
+      </c>
+      <c r="K11" s="1">
+        <v>41.23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>170985</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="6">
-        <v>126.33</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.7614</v>
-      </c>
-      <c r="E11" s="6">
-        <v>222.52</v>
-      </c>
-      <c r="F11" s="6">
-        <v>225.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="6">
-        <v>44</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.46</v>
-      </c>
-      <c r="E12" s="6">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="F12" s="6">
-        <v>67.76000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="8" t="s">
+      <c r="F12">
+        <v>40.66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12">
+        <v>1.77</v>
+      </c>
+      <c r="I12" s="1">
+        <v>71.97</v>
+      </c>
+      <c r="J12">
+        <v>1.82</v>
+      </c>
+      <c r="K12" s="1">
+        <v>74</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="6">
+        <v>256.38</v>
+      </c>
+      <c r="C17" s="6">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.7612</v>
+      </c>
+      <c r="E17" s="6">
+        <v>451.53</v>
+      </c>
+      <c r="F17" s="6">
+        <v>461.48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="9">
-        <v>170.33</v>
-      </c>
-      <c r="C13" s="9">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>286.76</v>
-      </c>
-      <c r="F13" s="9">
-        <v>293.73</v>
+      <c r="B18" s="6">
+        <v>113.42</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.4967</v>
+      </c>
+      <c r="E18" s="6">
+        <v>169.76</v>
+      </c>
+      <c r="F18" s="6">
+        <v>176.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="9">
+        <v>369.8</v>
+      </c>
+      <c r="C19" s="9">
+        <v>11</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="9">
+        <v>621.29</v>
+      </c>
+      <c r="F19" s="9">
+        <v>638.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -247,7 +247,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,12 +257,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,17 +306,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="70">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -73,25 +82,31 @@
     <t>2026-06-21</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>София България</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>Севлиево</t>
-  </si>
-  <si>
-    <t>Ямбол</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
+  </si>
+  <si>
+    <t>1173 Ямбол</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
   </si>
   <si>
     <t>B0847TK</t>
@@ -118,34 +133,79 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-06-01 09:16:45</t>
-  </si>
-  <si>
-    <t>2026-06-02 12:06:24</t>
-  </si>
-  <si>
-    <t>2026-06-05 16:47:49</t>
-  </si>
-  <si>
-    <t>2026-06-09 12:52:00</t>
-  </si>
-  <si>
-    <t>2026-06-11 14:45:14</t>
-  </si>
-  <si>
-    <t>2026-06-17 10:57:54</t>
-  </si>
-  <si>
-    <t>2026-06-19 00:11:07</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:22:22</t>
-  </si>
-  <si>
-    <t>2026-06-21 16:55:38</t>
-  </si>
-  <si>
-    <t>2026-06-21 19:45:05</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:16:00</t>
+  </si>
+  <si>
+    <t>12:06:00</t>
+  </si>
+  <si>
+    <t>16:48:00</t>
+  </si>
+  <si>
+    <t>12:51:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>10:57:00</t>
+  </si>
+  <si>
+    <t>00:11:00</t>
+  </si>
+  <si>
+    <t>15:22:00</t>
+  </si>
+  <si>
+    <t>16:55:00</t>
+  </si>
+  <si>
+    <t>19:44:00</t>
+  </si>
+  <si>
+    <t>15:41:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>3232716854 3232716854</t>
+  </si>
+  <si>
+    <t>3232765470 3232765470</t>
+  </si>
+  <si>
+    <t>3232908189 3232908189</t>
+  </si>
+  <si>
+    <t>3233096628 3233096628</t>
+  </si>
+  <si>
+    <t>3233204651 3233204651</t>
+  </si>
+  <si>
+    <t>3233475763 3233475763</t>
+  </si>
+  <si>
+    <t>3233554325 3233554325</t>
+  </si>
+  <si>
+    <t>3233594320 3233594320</t>
+  </si>
+  <si>
+    <t>3233683580 3233683580</t>
+  </si>
+  <si>
+    <t>3233683571 3233683571</t>
+  </si>
+  <si>
+    <t>3233944292 3233944292</t>
+  </si>
+  <si>
+    <t>3234099071 3234099071</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ</t>
@@ -563,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -572,14 +632,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -613,448 +676,635 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>41.4</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
         <v>1.52</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>62.93</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>65</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>26.36</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3">
         <v>1.77</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>46.66</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.82</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>47.98</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>40.86</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4">
         <v>1.77</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>72.31999999999999</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.82</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>74.37</v>
       </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
+        <v>21934</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>40.44</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5">
         <v>1.51</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>61.06</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>63.09</v>
       </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>22.35</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6">
         <v>1.76</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>39.34</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.81</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>40.45</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
       <c r="F7">
         <v>40.69</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
         <v>1.76</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>71.61</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.81</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>73.65000000000001</v>
       </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>24.91</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
         <v>1.76</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>43.84</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.81</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>45.09</v>
       </c>
-      <c r="K8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F9">
         <v>26.25</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
         <v>1.75</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>45.94</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.8</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>47.25</v>
       </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <v>22617</v>
+      </c>
+      <c r="N9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>24.68</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
         <v>1.47</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>36.28</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.52</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>37.51</v>
       </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10">
+        <v>23140</v>
+      </c>
+      <c r="N10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>40</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11">
         <v>1.74</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>69.59999999999999</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.79</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>71.59999999999999</v>
       </c>
-      <c r="K11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6">
-        <v>221.42</v>
-      </c>
-      <c r="C16" s="6">
-        <v>7</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.7582</v>
-      </c>
-      <c r="E16" s="6">
-        <v>389.31</v>
-      </c>
-      <c r="F16" s="6">
-        <v>400.39</v>
-      </c>
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11">
+        <v>23444</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>25.36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12">
+        <v>1.71</v>
+      </c>
+      <c r="I12" s="1">
+        <v>43.37</v>
+      </c>
+      <c r="J12">
+        <v>1.76</v>
+      </c>
+      <c r="K12" s="1">
+        <v>44.63</v>
+      </c>
+      <c r="L12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>43.57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>1.45</v>
+      </c>
+      <c r="I13" s="1">
+        <v>63.18</v>
+      </c>
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>65.36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="6">
-        <v>106.52</v>
-      </c>
-      <c r="C17" s="6">
-        <v>3</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.5046</v>
-      </c>
-      <c r="E17" s="6">
-        <v>160.27</v>
-      </c>
-      <c r="F17" s="6">
-        <v>165.6</v>
+      <c r="A17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="9">
-        <v>327.94</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9">
-        <v>549.58</v>
-      </c>
-      <c r="F18" s="9">
-        <v>565.99</v>
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6">
+        <v>246.78</v>
+      </c>
+      <c r="C18" s="6">
+        <v>8</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.7533</v>
+      </c>
+      <c r="E18" s="6">
+        <v>432.68</v>
+      </c>
+      <c r="F18" s="6">
+        <v>445.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6">
+        <v>150.09</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.4888</v>
+      </c>
+      <c r="E19" s="6">
+        <v>223.45</v>
+      </c>
+      <c r="F19" s="6">
+        <v>230.96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="9">
+        <v>396.87</v>
+      </c>
+      <c r="C20" s="9">
+        <v>12</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="9">
+        <v>656.13</v>
+      </c>
+      <c r="F20" s="9">
+        <v>675.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -67,16 +73,37 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
   </si>
   <si>
     <t>СB6072HO</t>
@@ -103,22 +130,67 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-02 18:18:30</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:25:47</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:23:52</t>
-  </si>
-  <si>
-    <t>2026-07-11 23:12:29</t>
-  </si>
-  <si>
-    <t>2026-07-14 22:00:43</t>
-  </si>
-  <si>
-    <t>2026-07-15 19:47:02</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:18:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>23:12:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>19:47:00</t>
+  </si>
+  <si>
+    <t>13:23:00</t>
+  </si>
+  <si>
+    <t>15:25:00</t>
+  </si>
+  <si>
+    <t>16:43:00</t>
+  </si>
+  <si>
+    <t>09:28:00</t>
+  </si>
+  <si>
+    <t>3234201871 3234201871</t>
+  </si>
+  <si>
+    <t>3234586011 3234586011</t>
+  </si>
+  <si>
+    <t>3234607156 3234607156</t>
+  </si>
+  <si>
+    <t>3234592629 3234592629</t>
+  </si>
+  <si>
+    <t>3234800797 3234800797</t>
+  </si>
+  <si>
+    <t>3234818190 3234818190</t>
+  </si>
+  <si>
+    <t>3235040899 3235040899</t>
+  </si>
+  <si>
+    <t>3235151201 3235151201</t>
+  </si>
+  <si>
+    <t>3235234828 3235234828</t>
+  </si>
+  <si>
+    <t>3235336338 3235336338</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ</t>
@@ -536,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -545,15 +617,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -590,326 +664,544 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>40.02</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
         <v>1.71</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>68.43000000000001</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.76</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>70.44</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2">
         <v>23849</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>27.13</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3">
         <v>1.71</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>46.39</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.76</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>47.75</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>32.13</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4">
         <v>1.71</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>54.94</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.76</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>56.55</v>
       </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4">
         <v>24204</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>40.47</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5">
         <v>1.7</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>68.8</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.75</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>70.81999999999999</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5">
         <v>24802</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>28.98</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6">
         <v>1.7</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>49.27</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.75</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>50.72</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>43.26</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7">
         <v>1.44</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>62.29</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.49</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>64.45999999999999</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>29.06</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>1.76</v>
+      </c>
+      <c r="I8" s="1">
+        <v>51.15</v>
+      </c>
+      <c r="J8">
+        <v>1.81</v>
+      </c>
+      <c r="K8" s="1">
+        <v>52.6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="L7">
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>25.22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>1.74</v>
+      </c>
+      <c r="I9" s="1">
+        <v>43.88</v>
+      </c>
+      <c r="J9">
+        <v>1.79</v>
+      </c>
+      <c r="K9" s="1">
+        <v>45.14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="F10">
+        <v>41.01</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10">
+        <v>1.76</v>
+      </c>
+      <c r="I10" s="1">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="J10">
+        <v>1.81</v>
+      </c>
+      <c r="K10" s="1">
+        <v>74.23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
+        <v>26126</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>17.19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>1.79</v>
+      </c>
+      <c r="I11" s="1">
+        <v>30.77</v>
+      </c>
+      <c r="J11">
+        <v>1.84</v>
+      </c>
+      <c r="K11" s="1">
+        <v>31.63</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6">
+        <v>281.21</v>
+      </c>
+      <c r="C16" s="6">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.7276</v>
+      </c>
+      <c r="E16" s="6">
+        <v>485.81</v>
+      </c>
+      <c r="F16" s="6">
+        <v>499.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="6">
-        <v>168.73</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.7059</v>
-      </c>
-      <c r="E12" s="6">
-        <v>287.83</v>
-      </c>
-      <c r="F12" s="6">
-        <v>296.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="B17" s="6">
         <v>43.26</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D17" s="7">
         <v>1.4399</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E17" s="6">
         <v>62.29</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F17" s="6">
         <v>64.45999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="9">
-        <v>211.99</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>350.12</v>
-      </c>
-      <c r="F14" s="9">
-        <v>360.74</v>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="9">
+        <v>324.47</v>
+      </c>
+      <c r="C18" s="9">
+        <v>10</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9">
+        <v>548.1</v>
+      </c>
+      <c r="F18" s="9">
+        <v>564.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -217,7 +217,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="7">
-        <v>1.7276</v>
+        <v>1.72757</v>
       </c>
       <c r="E16" s="6">
         <v>485.81</v>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="7">
-        <v>1.4399</v>
+        <v>1.439898</v>
       </c>
       <c r="E17" s="6">
         <v>62.29</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -608,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -621,13 +624,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,450 +673,483 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2">
+        <v>40.023</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
+        <v>1.649</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="J2">
+        <v>68.43933</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L2" s="1">
+        <v>70.44047999999999</v>
+      </c>
+      <c r="M2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2">
+        <v>23849</v>
+      </c>
+      <c r="O2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>27.131</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3">
+        <v>1.629</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="J3">
+        <v>46.39401</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L3" s="1">
+        <v>47.75056</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4">
+        <v>32.131</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4">
+        <v>1.629</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="J4">
+        <v>54.94401</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L4" s="1">
+        <v>56.55056</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4">
+        <v>24204</v>
+      </c>
+      <c r="O4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5">
+        <v>40.469</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5">
+        <v>1.629</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="J5">
+        <v>68.79730000000001</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L5" s="1">
+        <v>70.82075</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5">
+        <v>24802</v>
+      </c>
+      <c r="O5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6">
+        <v>28.983</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6">
+        <v>1.629</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="J6">
+        <v>49.2711</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L6" s="1">
+        <v>50.72025</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>43.262</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>1.369</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="J7">
+        <v>62.29728</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L7" s="1">
+        <v>64.46038</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>29.061</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>1.629</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="J8">
+        <v>51.14736</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="L8" s="1">
+        <v>52.60041</v>
+      </c>
+      <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>25.218</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>1.629</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="J9">
+        <v>43.87932</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>45.14022</v>
+      </c>
+      <c r="M9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>41.011</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
+        <v>1.649</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="J10">
+        <v>72.17936</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="L10" s="1">
+        <v>74.22991</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10">
+        <v>26126</v>
+      </c>
+      <c r="O10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2">
-        <v>40.02</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2">
-        <v>1.71</v>
-      </c>
-      <c r="I2" s="1">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="J2">
-        <v>1.76</v>
-      </c>
-      <c r="K2" s="1">
-        <v>70.44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2">
-        <v>23849</v>
-      </c>
-      <c r="N2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>27.13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3">
-        <v>1.71</v>
-      </c>
-      <c r="I3" s="1">
-        <v>46.39</v>
-      </c>
-      <c r="J3">
-        <v>1.76</v>
-      </c>
-      <c r="K3" s="1">
-        <v>47.75</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>32.13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4">
-        <v>1.71</v>
-      </c>
-      <c r="I4" s="1">
-        <v>54.94</v>
-      </c>
-      <c r="J4">
-        <v>1.76</v>
-      </c>
-      <c r="K4" s="1">
-        <v>56.55</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4">
-        <v>24204</v>
-      </c>
-      <c r="N4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5">
-        <v>40.47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5">
-        <v>1.7</v>
-      </c>
-      <c r="I5" s="1">
-        <v>68.8</v>
-      </c>
-      <c r="J5">
-        <v>1.75</v>
-      </c>
-      <c r="K5" s="1">
-        <v>70.81999999999999</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5">
-        <v>24802</v>
-      </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>28.98</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6">
-        <v>1.7</v>
-      </c>
-      <c r="I6" s="1">
-        <v>49.27</v>
-      </c>
-      <c r="J6">
-        <v>1.75</v>
-      </c>
-      <c r="K6" s="1">
-        <v>50.72</v>
-      </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E11" t="s">
         <v>37</v>
-      </c>
-      <c r="F7">
-        <v>43.26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7">
-        <v>1.44</v>
-      </c>
-      <c r="I7" s="1">
-        <v>62.29</v>
-      </c>
-      <c r="J7">
-        <v>1.49</v>
-      </c>
-      <c r="K7" s="1">
-        <v>64.45999999999999</v>
-      </c>
-      <c r="L7" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>29.06</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8">
-        <v>1.76</v>
-      </c>
-      <c r="I8" s="1">
-        <v>51.15</v>
-      </c>
-      <c r="J8">
-        <v>1.81</v>
-      </c>
-      <c r="K8" s="1">
-        <v>52.6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9">
-        <v>25.22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>1.74</v>
-      </c>
-      <c r="I9" s="1">
-        <v>43.88</v>
-      </c>
-      <c r="J9">
-        <v>1.79</v>
-      </c>
-      <c r="K9" s="1">
-        <v>45.14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10">
-        <v>41.01</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10">
-        <v>1.76</v>
-      </c>
-      <c r="I10" s="1">
-        <v>72.18000000000001</v>
-      </c>
-      <c r="J10">
-        <v>1.81</v>
-      </c>
-      <c r="K10" s="1">
-        <v>74.23</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10">
-        <v>26126</v>
-      </c>
-      <c r="N10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
       </c>
       <c r="F11">
         <v>17.19</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11">
+        <v>1.649</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.79</v>
       </c>
-      <c r="I11" s="1">
-        <v>30.77</v>
-      </c>
       <c r="J11">
+        <v>30.7701</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.84</v>
       </c>
-      <c r="K11" s="1">
-        <v>31.63</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>31.6296</v>
+      </c>
+      <c r="M11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1121,41 +1157,41 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6">
-        <v>281.21</v>
+        <v>281.217</v>
       </c>
       <c r="C16" s="6">
         <v>9</v>
       </c>
       <c r="D16" s="7">
-        <v>1.72757</v>
+        <v>1.727569</v>
       </c>
       <c r="E16" s="6">
-        <v>485.81</v>
+        <v>485.82</v>
       </c>
       <c r="F16" s="6">
         <v>499.88</v>
@@ -1163,19 +1199,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="6">
-        <v>43.26</v>
+        <v>43.262</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
       </c>
       <c r="D17" s="7">
-        <v>1.439898</v>
+        <v>1.44</v>
       </c>
       <c r="E17" s="6">
-        <v>62.29</v>
+        <v>62.3</v>
       </c>
       <c r="F17" s="6">
         <v>64.45999999999999</v>
@@ -1183,17 +1219,17 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="9">
-        <v>324.47</v>
+        <v>324.479</v>
       </c>
       <c r="C18" s="9">
         <v>10</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="9">
-        <v>548.1</v>
+        <v>548.12</v>
       </c>
       <c r="F18" s="9">
         <v>564.34</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="65">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -219,8 +216,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -313,10 +310,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -624,13 +621,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -673,483 +670,450 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>40.023</v>
       </c>
       <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
+        <v>1.71</v>
+      </c>
+      <c r="I2" s="1">
+        <v>68.43899999999999</v>
+      </c>
+      <c r="J2">
+        <v>1.76</v>
+      </c>
+      <c r="K2" s="1">
+        <v>70.44</v>
+      </c>
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="H2">
-        <v>1.649</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="J2">
-        <v>68.43933</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L2" s="1">
-        <v>70.44047999999999</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>23849</v>
       </c>
-      <c r="O2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>27.131</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3">
-        <v>1.629</v>
+        <v>1.71</v>
       </c>
       <c r="I3" s="1">
-        <v>1.71</v>
+        <v>46.394</v>
       </c>
       <c r="J3">
-        <v>46.39401</v>
+        <v>1.76</v>
       </c>
       <c r="K3" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L3" s="1">
-        <v>47.75056</v>
-      </c>
-      <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3">
+        <v>47.751</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>32.131</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4">
-        <v>1.629</v>
+        <v>1.71</v>
       </c>
       <c r="I4" s="1">
-        <v>1.71</v>
+        <v>54.944</v>
       </c>
       <c r="J4">
-        <v>54.94401</v>
+        <v>1.76</v>
       </c>
       <c r="K4" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L4" s="1">
-        <v>56.55056</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4">
+        <v>56.551</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4">
         <v>24204</v>
       </c>
-      <c r="O4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>40.469</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5">
-        <v>1.629</v>
+        <v>1.7</v>
       </c>
       <c r="I5" s="1">
-        <v>1.7</v>
+        <v>68.797</v>
       </c>
       <c r="J5">
-        <v>68.79730000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K5" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L5" s="1">
-        <v>70.82075</v>
-      </c>
-      <c r="M5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5">
+        <v>70.821</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5">
         <v>24802</v>
       </c>
-      <c r="O5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>28.983</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6">
-        <v>1.629</v>
+        <v>1.7</v>
       </c>
       <c r="I6" s="1">
-        <v>1.7</v>
+        <v>49.271</v>
       </c>
       <c r="J6">
-        <v>49.2711</v>
+        <v>1.75</v>
       </c>
       <c r="K6" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L6" s="1">
-        <v>50.72025</v>
-      </c>
-      <c r="M6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6">
+        <v>50.72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>43.262</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7">
-        <v>1.369</v>
+        <v>1.44</v>
       </c>
       <c r="I7" s="1">
-        <v>1.44</v>
+        <v>62.297</v>
       </c>
       <c r="J7">
-        <v>62.29728</v>
+        <v>1.49</v>
       </c>
       <c r="K7" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L7" s="1">
-        <v>64.46038</v>
-      </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>29.061</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8">
-        <v>1.629</v>
+        <v>1.76</v>
       </c>
       <c r="I8" s="1">
-        <v>1.76</v>
+        <v>51.147</v>
       </c>
       <c r="J8">
-        <v>51.14736</v>
+        <v>1.81</v>
       </c>
       <c r="K8" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L8" s="1">
-        <v>52.60041</v>
-      </c>
-      <c r="M8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8">
+        <v>52.6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>25.218</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>1.629</v>
+        <v>1.74</v>
       </c>
       <c r="I9" s="1">
-        <v>1.74</v>
+        <v>43.879</v>
       </c>
       <c r="J9">
-        <v>43.87932</v>
+        <v>1.79</v>
       </c>
       <c r="K9" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L9" s="1">
-        <v>45.14022</v>
-      </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9">
+        <v>45.14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>41.011</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>1.649</v>
+        <v>1.76</v>
       </c>
       <c r="I10" s="1">
-        <v>1.76</v>
+        <v>72.179</v>
       </c>
       <c r="J10">
-        <v>72.17936</v>
+        <v>1.81</v>
       </c>
       <c r="K10" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L10" s="1">
-        <v>74.22991</v>
-      </c>
-      <c r="M10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10">
+        <v>74.23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
         <v>26126</v>
       </c>
-      <c r="O10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>17.19</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11">
-        <v>1.649</v>
+        <v>1.79</v>
       </c>
       <c r="I11" s="1">
-        <v>1.79</v>
+        <v>30.77</v>
       </c>
       <c r="J11">
-        <v>30.7701</v>
+        <v>1.84</v>
       </c>
       <c r="K11" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="L11" s="1">
-        <v>31.6296</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11">
+        <v>31.63</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1157,69 +1121,69 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6">
         <v>281.217</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>9</v>
       </c>
       <c r="D16" s="7">
-        <v>1.727569</v>
-      </c>
-      <c r="E16" s="6">
+        <v>1.728</v>
+      </c>
+      <c r="E16" s="7">
         <v>485.82</v>
       </c>
-      <c r="F16" s="6">
-        <v>499.88</v>
+      <c r="F16" s="7">
+        <v>499.883</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6">
         <v>43.262</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>1</v>
       </c>
       <c r="D17" s="7">
         <v>1.44</v>
       </c>
-      <c r="E17" s="6">
-        <v>62.3</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="7">
+        <v>62.297</v>
+      </c>
+      <c r="F17" s="7">
         <v>64.45999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="9">
         <v>324.479</v>
@@ -1229,10 +1193,10 @@
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="9">
-        <v>548.12</v>
+        <v>548.117</v>
       </c>
       <c r="F18" s="9">
-        <v>564.34</v>
+        <v>564.343</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ/ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ.xlsx
@@ -697,10 +697,10 @@
         <v>38</v>
       </c>
       <c r="H2" s="1">
-        <v>1.636</v>
+        <v>1.76</v>
       </c>
       <c r="I2" s="1">
-        <v>43.174</v>
+        <v>46.446</v>
       </c>
       <c r="J2" s="1">
         <v>1.81</v>
@@ -741,10 +741,10 @@
         <v>38</v>
       </c>
       <c r="H3" s="1">
-        <v>1.409</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="1">
-        <v>58.699</v>
+        <v>62.49</v>
       </c>
       <c r="J3" s="1">
         <v>1.55</v>
@@ -785,10 +785,10 @@
         <v>38</v>
       </c>
       <c r="H4" s="1">
-        <v>1.636</v>
+        <v>1.79</v>
       </c>
       <c r="I4" s="1">
-        <v>57.734</v>
+        <v>63.169</v>
       </c>
       <c r="J4" s="1">
         <v>1.84</v>
@@ -829,10 +829,10 @@
         <v>38</v>
       </c>
       <c r="H5" s="1">
-        <v>1.636</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1">
-        <v>65.914</v>
+        <v>70.91</v>
       </c>
       <c r="J5" s="1">
         <v>1.81</v>
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="H6" s="1">
-        <v>1.636</v>
+        <v>1.77</v>
       </c>
       <c r="I6" s="1">
-        <v>46.79</v>
+        <v>50.622</v>
       </c>
       <c r="J6" s="1">
         <v>1.82</v>
@@ -917,10 +917,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="1">
-        <v>1.419</v>
+        <v>1.52</v>
       </c>
       <c r="I7" s="1">
-        <v>55.341</v>
+        <v>59.28</v>
       </c>
       <c r="J7" s="1">
         <v>1.57</v>
@@ -961,10 +961,10 @@
         <v>38</v>
       </c>
       <c r="H8" s="1">
-        <v>1.646</v>
+        <v>1.79</v>
       </c>
       <c r="I8" s="1">
-        <v>60.03</v>
+        <v>65.28100000000001</v>
       </c>
       <c r="J8" s="1">
         <v>1.84</v>
@@ -1005,10 +1005,10 @@
         <v>38</v>
       </c>
       <c r="H9" s="1">
-        <v>1.646</v>
+        <v>1.78</v>
       </c>
       <c r="I9" s="1">
-        <v>66.84399999999999</v>
+        <v>72.286</v>
       </c>
       <c r="J9" s="1">
         <v>1.83</v>
@@ -1049,10 +1049,10 @@
         <v>38</v>
       </c>
       <c r="H10" s="1">
-        <v>1.679</v>
+        <v>1.79</v>
       </c>
       <c r="I10" s="1">
-        <v>44.88</v>
+        <v>47.847</v>
       </c>
       <c r="J10" s="1">
         <v>1.84</v>
@@ -1093,10 +1093,10 @@
         <v>38</v>
       </c>
       <c r="H11" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I11" s="1">
-        <v>57.373</v>
+        <v>61.4</v>
       </c>
       <c r="J11" s="1">
         <v>1.59</v>
@@ -1155,10 +1155,10 @@
         <v>7</v>
       </c>
       <c r="D16" s="8">
-        <v>1.64419</v>
+        <v>1.77729</v>
       </c>
       <c r="E16" s="6">
-        <v>385.37</v>
+        <v>416.56</v>
       </c>
       <c r="F16" s="6">
         <v>428.28</v>
@@ -1175,10 +1175,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="8">
-        <v>1.42216</v>
+        <v>1.5197</v>
       </c>
       <c r="E17" s="6">
-        <v>171.41</v>
+        <v>183.17</v>
       </c>
       <c r="F17" s="6">
         <v>189.2</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="10">
-        <v>556.78</v>
+        <v>599.73</v>
       </c>
       <c r="F18" s="10">
         <v>617.48</v>
